--- a/artfynd/A 56462-2024 artfynd.xlsx
+++ b/artfynd/A 56462-2024 artfynd.xlsx
@@ -675,55 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104298843</v>
+        <v>112161615</v>
       </c>
       <c r="B2" t="n">
-        <v>12638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101954</v>
+        <v>100808</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större svartbagge</t>
+          <t>Svart ögonknäppare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Upis ceramboides</t>
+          <t>Denticollis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Paykull, 1800)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Harrsjön, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795140.5626225786</v>
+        <v>795137</v>
       </c>
       <c r="R2" t="n">
-        <v>7177343.265403412</v>
+        <v>7177320</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>TF10, björkdominerad naturskog, spritlagt prov</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,20 +773,15 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Björkdominerad skog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>riktat sök björkhögstubbe och björklåga med fnösketicka</t>
-        </is>
-      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Roger Mugerwa Pettersson</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -799,23 +793,14 @@
           <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Uppföljning av större svartbagge i AC</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>112161641</v>
       </c>
       <c r="B3" t="n">
-        <v>8712</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,12 +927,7 @@
         <v>112161643</v>
       </c>
       <c r="B4" t="n">
-        <v>12389</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,52 +1051,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112161632</v>
+        <v>104298844</v>
       </c>
       <c r="B5" t="n">
-        <v>12119</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101642</v>
+        <v>101377</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korthornad ögonbagge</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudanidorus pentatomus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Thomson, 1864)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1125,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795140</v>
+        <v>795200</v>
       </c>
       <c r="R5" t="n">
-        <v>7177334</v>
+        <v>7177341</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1155,17 +1133,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>TF9, björkdominerad naturskog</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,15 +1157,20 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Roger Mugerwa Pettersson</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Björkdominerad skog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stående död björk med &gt;10 kläckhål stekelbock</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1194,19 +1182,18 @@
           <t>Roger Mugerwa Pettersson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Uppföljning av större svartbagge i AC</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112161615</v>
+        <v>112161632</v>
       </c>
       <c r="B6" t="n">
-        <v>8712</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,21 +1201,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100808</v>
+        <v>101642</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart ögonknäppare</t>
+          <t>Korthornad ögonbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Denticollis borealis</t>
+          <t>Pseudanidorus pentatomus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Paykull, 1800)</t>
+          <t>(Thomson, 1864)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1252,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795137</v>
+        <v>795140</v>
       </c>
       <c r="R6" t="n">
-        <v>7177320</v>
+        <v>7177334</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1292,7 +1279,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>TF10, björkdominerad naturskog, spritlagt prov</t>
+          <t>TF9, björkdominerad naturskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,12 +1315,7 @@
         <v>112161633</v>
       </c>
       <c r="B7" t="n">
-        <v>12119</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56462-2024 artfynd.xlsx
+++ b/artfynd/A 56462-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112161615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112161641</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112161643</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1187,6 +1207,11 @@
           <t>Uppföljning av större svartbagge i AC</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104298844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1309,6 +1334,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112161632</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1436,8 +1466,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112161633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>